--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>{.inventoryDirectionName}</t>
   </si>
   <si>
-    <t>{.typeName}</t>
+    <t>{.outTypeName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1112,8 +1112,9 @@
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="23.375" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="23.25" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="15.75" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>出库单号</t>
   </si>
@@ -37,6 +37,9 @@
     <t>客户</t>
   </si>
   <si>
+    <t>跟踪号</t>
+  </si>
+  <si>
     <t>库存方向</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>审核完成时间</t>
   </si>
   <si>
+    <t>领料部门</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>{.customerName}</t>
   </si>
   <si>
+    <t>{.trackNo}</t>
+  </si>
+  <si>
     <t>{.inventoryDirectionName}</t>
   </si>
   <si>
@@ -131,6 +140,9 @@
   </si>
   <si>
     <t>{.approveTime}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1107,28 +1119,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="23.375" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="23.25" customWidth="1"/>
-    <col min="6" max="6" width="10.625" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="12" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="25.5" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="24.5" customWidth="1"/>
+    <col min="3" max="4" width="23.375" customWidth="1"/>
+    <col min="5" max="5" width="19.75" customWidth="1"/>
+    <col min="6" max="6" width="23.25" customWidth="1"/>
+    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="15.75" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
+    <col min="13" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="25.5" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
+    <col min="18" max="19" width="11.75" customWidth="1"/>
+    <col min="20" max="20" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,13 +1165,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1183,61 +1195,73 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>出库单号</t>
   </si>
@@ -76,6 +76,12 @@
     <t>流程申请单号</t>
   </si>
   <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>审核人(最新)</t>
   </si>
   <si>
@@ -134,6 +140,12 @@
   </si>
   <si>
     <t>{.processApplyCode}</t>
+  </si>
+  <si>
+    <t>{.usage}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1119,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1134,13 +1146,13 @@
     <col min="11" max="11" width="10.5" customWidth="1"/>
     <col min="13" max="14" width="17.25" customWidth="1"/>
     <col min="15" max="15" width="25.5" customWidth="1"/>
-    <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="14.875" customWidth="1"/>
-    <col min="18" max="19" width="11.75" customWidth="1"/>
-    <col min="20" max="20" width="24.5" customWidth="1"/>
+    <col min="16" max="18" width="13.5" customWidth="1"/>
+    <col min="19" max="19" width="14.875" customWidth="1"/>
+    <col min="20" max="21" width="11.75" customWidth="1"/>
+    <col min="22" max="22" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,67 +1213,79 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
